--- a/fx_pipeline/data/gold/marts/excel/gold_weekly_currency_summary.xlsx
+++ b/fx_pipeline/data/gold/marts/excel/gold_weekly_currency_summary.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.4029</v>
+        <v>1.39636</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4216</v>
+        <v>1.4013</v>
       </c>
       <c r="D2" t="n">
         <v>1.3934</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4216</v>
+        <v>1.4013</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3934</v>
+        <v>1.3957</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0282</v>
+        <v>-0.005600000000000049</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.983680360157569</v>
+        <v>-0.3996289160065688</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.3757</v>
+        <v>1.37068</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3845</v>
+        <v>1.3782</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3672</v>
+        <v>1.3657</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3845</v>
+        <v>1.3782</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3672</v>
+        <v>1.3657</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.01730000000000009</v>
+        <v>-0.01250000000000018</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.249548573492242</v>
+        <v>-0.9069801189958044</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8498300000000001</v>
+        <v>0.849098</v>
       </c>
       <c r="C4" t="n">
-        <v>0.85587</v>
+        <v>0.85034</v>
       </c>
       <c r="D4" t="n">
         <v>0.84767</v>
       </c>
       <c r="E4" t="n">
-        <v>0.85587</v>
+        <v>0.8489</v>
       </c>
       <c r="F4" t="n">
-        <v>0.84767</v>
+        <v>0.84983</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.008199999999999985</v>
+        <v>0.0009299999999999864</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.958089429469427</v>
+        <v>0.1095535398751309</v>
       </c>
     </row>
     <row r="5">
@@ -549,25 +549,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.739468</v>
+        <v>0.739016</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7451</v>
+        <v>0.7401799999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.73699</v>
+        <v>0.73799</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7451</v>
+        <v>0.73799</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7389</v>
+        <v>0.73965</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.006199999999999983</v>
+        <v>0.001659999999999995</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8321030734129625</v>
+        <v>0.224935297226249</v>
       </c>
     </row>
     <row r="6">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93.184</v>
+        <v>93.21599999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>93.44</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="D6" t="n">
         <v>92.81999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>93.33</v>
+        <v>93.44</v>
       </c>
       <c r="F6" t="n">
-        <v>92.81999999999999</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5100000000000051</v>
+        <v>0.07000000000000739</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5464480874316995</v>
+        <v>0.07491438356165174</v>
       </c>
     </row>
     <row r="7">
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>159.176</v>
+        <v>159.03</v>
       </c>
       <c r="C7" t="n">
-        <v>159.83</v>
+        <v>159.13</v>
       </c>
       <c r="D7" t="n">
-        <v>158.85</v>
+        <v>158.91</v>
       </c>
       <c r="E7" t="n">
-        <v>159.83</v>
+        <v>159.09</v>
       </c>
       <c r="F7" t="n">
-        <v>159.13</v>
+        <v>159.04</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7000000000000171</v>
+        <v>-0.05000000000001137</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4379653381718182</v>
+        <v>-0.03142875102144155</v>
       </c>
     </row>
   </sheetData>
